--- a/taxa_media/input/fundos.xlsx
+++ b/taxa_media/input/fundos.xlsx
@@ -55,12 +55,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,23 +425,23 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" style="3" min="1" max="1"/>
+    <col width="8" customWidth="1" style="3" min="2" max="2"/>
+    <col width="40" customWidth="1" style="3" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>fundo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>rodar</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
@@ -462,7 +458,6 @@
           <t>S</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -480,26 +475,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" style="3" min="1" max="1"/>
+    <col width="8" customWidth="1" style="3" min="2" max="2"/>
+    <col width="95" customWidth="1" style="3" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>RFTP_CD</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>incluir</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -525,83 +520,168 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LTN-O</t>
+          <t>LFT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>compromissada over (LTN)</t>
+          <t>Tesouro Selic (LFT) em definitivo: grupo SELIC+</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NTN-O</t>
+          <t>LTN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>compromissada over (NTN)</t>
+          <t>Tesouro prefixado (LTN) em definitivo: grupo Pré (código provável: confira o RFTP_CD na VCRA)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LFT O</t>
+          <t>NTN-B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>compromissada over (LFT)</t>
+          <t>Tesouro IPCA+ (NTN-B) em definitivo: grupo IPCA+ (código provável: confira o RFTP_CD na VCRA)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CRIOP</t>
+          <t>NTN-F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>compromissada com lastro em CRI (usa o código do CRI de lastro)</t>
+          <t>Tesouro prefixado com juros (NTN-F): grupo Pré (código provável: confira o RFTP_CD na VCRA)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>FIDC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cotas de FIDC da posição (código 5 + letra; não estão na VCRA): taxa do Lake ou do cadastro</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LTN-O</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>compromissada over (LTN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NTN-O</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>compromissada over (NTN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LFT O</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>compromissada over (LFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CRIOP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>compromissada com lastro em CRI (usa o código do CRI de lastro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>CRILA</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>compromissada com lastro em CRI</t>
         </is>
@@ -626,35 +706,35 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="3" max="3"/>
+    <col width="8" customWidth="1" style="3" min="4" max="4"/>
+    <col width="90" customWidth="1" style="3" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>fundo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>taxa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>aplicar</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>motivo</t>
         </is>
@@ -701,10 +781,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" style="3" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,55 +794,74 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Fundos: um fundo por linha (codigo_IAM_fundo). rodar = N pula o fundo; vazio roda.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Tipos: RFTP_CD da VCRAOPRF e se ele entra no cálculo (incluir = S).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tipo que aparecer na VCRA e não estiver aqui sai como aviso 'Tipo novo' e fica fora.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Compromissadas ficam com N: a CRIOP usa o código do CRI de lastro e somaria a compromissada ao CRI.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Só entram papéis atrelados ao CDI: IPCA, pré e SELIC ficam fora com aviso, mesmo com incluir = S.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Grupos pelo indexador: CDI (%CDI ou CDI+), SELIC (SELIC+), pré (Pré) e IPCA (IPCA+); IGP-M, dólar e outros ficam fora com aviso.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   IPCA+ sai à parte: só entra na carteira em CDI+ equivalente com o IPCA projetado (--ipca).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   FIDC não é RFTP_CD: são as cotas de FIDC da posição (código 5 + letra). Com N, ficam fora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Correções: taxa corrigida de um lote (CD) do fundo. aplicar = S (ou vazio) para valer.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Taxa na convenção do grupo do ativo: CDI+ = spread em % a.a. (ex.: 2,5); %CDI = % do CDI (ex.: 101,3).</t>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Taxa na convenção do grupo do ativo: CDI+, SELIC+ e IPCA+ = spread em % a.a. (ex.: 2,5); %CDI = % do CDI (ex.: 101,3); Pré = taxa % a.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Na cota de FIDC, o CD é o próprio código da cota (ex.: 5BVAIMZA).</t>
         </is>
       </c>
     </row>
